--- a/sources/table_normalization/xlsx/education-table30.xlsx
+++ b/sources/table_normalization/xlsx/education-table30.xlsx
@@ -148,7 +148,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -158,12 +158,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -204,7 +198,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -215,9 +209,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal_Sheet1" xfId="1"/>
@@ -771,7 +763,7 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -821,7 +813,7 @@
       <c r="O2" s="3">
         <v>1</v>
       </c>
-      <c r="T2" s="7">
+      <c r="T2" s="2">
         <f t="shared" ref="T2:T9" si="0">SUM(D2:S2)</f>
         <v>21</v>
       </c>
@@ -876,7 +868,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
-      <c r="T3" s="7">
+      <c r="T3" s="2">
         <v>19</v>
       </c>
     </row>
@@ -930,7 +922,7 @@
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
-      <c r="T4" s="7">
+      <c r="T4" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -985,7 +977,7 @@
       <c r="S5" s="2">
         <v>2</v>
       </c>
-      <c r="T5" s="7">
+      <c r="T5" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -1040,7 +1032,7 @@
       <c r="S6" s="3">
         <v>2</v>
       </c>
-      <c r="T6" s="7">
+      <c r="T6" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1095,7 +1087,7 @@
       <c r="S7" s="3">
         <v>1</v>
       </c>
-      <c r="T7" s="7">
+      <c r="T7" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1150,7 +1142,7 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-      <c r="T8" s="7">
+      <c r="T8" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1205,7 +1197,7 @@
       <c r="S9" s="2">
         <v>2</v>
       </c>
-      <c r="T9" s="7">
+      <c r="T9" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -1256,7 +1248,7 @@
       <c r="O10" s="3">
         <v>2</v>
       </c>
-      <c r="T10" s="7">
+      <c r="T10" s="2">
         <v>24</v>
       </c>
     </row>
@@ -1306,7 +1298,7 @@
       <c r="O11" s="3">
         <v>2</v>
       </c>
-      <c r="T11" s="7">
+      <c r="T11" s="2">
         <v>14</v>
       </c>
     </row>
@@ -1356,7 +1348,7 @@
       <c r="O12" s="3">
         <v>3</v>
       </c>
-      <c r="T12" s="7">
+      <c r="T12" s="2">
         <f t="shared" ref="T12:T17" si="1">SUM(D12:S12)</f>
         <v>19</v>
       </c>
@@ -1411,7 +1403,7 @@
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
-      <c r="T13" s="7">
+      <c r="T13" s="2">
         <v>17</v>
       </c>
     </row>
@@ -1461,7 +1453,7 @@
       <c r="O14" s="3">
         <v>2</v>
       </c>
-      <c r="T14" s="7">
+      <c r="T14" s="2">
         <v>10</v>
       </c>
     </row>
@@ -1515,7 +1507,7 @@
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
-      <c r="T15" s="7">
+      <c r="T15" s="2">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
@@ -1570,7 +1562,7 @@
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
-      <c r="T16" s="7">
+      <c r="T16" s="2">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
@@ -1625,7 +1617,7 @@
       <c r="S17" s="3">
         <v>1</v>
       </c>
-      <c r="T17" s="7">
+      <c r="T17" s="2">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -1680,7 +1672,7 @@
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
-      <c r="T18" s="7">
+      <c r="T18" s="2">
         <v>24</v>
       </c>
     </row>
@@ -1734,7 +1726,7 @@
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
-      <c r="T19" s="7">
+      <c r="T19" s="2">
         <f t="shared" ref="T19:T42" si="2">SUM(D19:S19)</f>
         <v>31</v>
       </c>
@@ -1785,7 +1777,7 @@
       <c r="O20" s="3">
         <v>3</v>
       </c>
-      <c r="T20" s="7">
+      <c r="T20" s="2">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
@@ -1840,7 +1832,7 @@
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
-      <c r="T21" s="7">
+      <c r="T21" s="2">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
@@ -1895,7 +1887,7 @@
       <c r="S22" s="2">
         <v>0</v>
       </c>
-      <c r="T22" s="7">
+      <c r="T22" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1946,7 +1938,7 @@
       <c r="O23" s="3">
         <v>2</v>
       </c>
-      <c r="T23" s="7">
+      <c r="T23" s="2">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
@@ -2001,7 +1993,7 @@
       <c r="S24" s="3">
         <v>1</v>
       </c>
-      <c r="T24" s="7">
+      <c r="T24" s="2">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
@@ -2052,7 +2044,7 @@
       <c r="O25" s="3">
         <v>2</v>
       </c>
-      <c r="T25" s="7">
+      <c r="T25" s="2">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
@@ -2107,7 +2099,7 @@
       <c r="S26" s="2">
         <v>2</v>
       </c>
-      <c r="T26" s="7">
+      <c r="T26" s="2">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
@@ -2158,7 +2150,7 @@
       <c r="O27" s="3">
         <v>1</v>
       </c>
-      <c r="T27" s="7">
+      <c r="T27" s="2">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
@@ -2213,7 +2205,7 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-      <c r="T28" s="7">
+      <c r="T28" s="2">
         <f t="shared" si="2"/>
         <v>-2</v>
       </c>
@@ -2264,7 +2256,7 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="7">
+      <c r="T29" s="2">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
@@ -2315,7 +2307,7 @@
       <c r="O30" s="3">
         <v>2</v>
       </c>
-      <c r="T30" s="7">
+      <c r="T30" s="2">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
@@ -2366,7 +2358,7 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="T31" s="7">
+      <c r="T31" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2417,7 +2409,7 @@
       <c r="O32" s="3">
         <v>2</v>
       </c>
-      <c r="T32" s="7">
+      <c r="T32" s="2">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
@@ -2472,7 +2464,7 @@
       <c r="S33" s="3">
         <v>2</v>
       </c>
-      <c r="T33" s="7">
+      <c r="T33" s="2">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
@@ -2523,7 +2515,7 @@
       <c r="O34" s="3">
         <v>2</v>
       </c>
-      <c r="T34" s="7">
+      <c r="T34" s="2">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
@@ -2578,7 +2570,7 @@
       <c r="S35" s="3">
         <v>2</v>
       </c>
-      <c r="T35" s="7">
+      <c r="T35" s="2">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
@@ -2629,7 +2621,7 @@
       <c r="O36" s="3">
         <v>3</v>
       </c>
-      <c r="T36" s="7">
+      <c r="T36" s="2">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
@@ -2684,7 +2676,7 @@
       <c r="S37" s="3">
         <v>1</v>
       </c>
-      <c r="T37" s="7">
+      <c r="T37" s="2">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
@@ -2739,7 +2731,7 @@
       <c r="S38" s="3">
         <v>0</v>
       </c>
-      <c r="T38" s="7">
+      <c r="T38" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2790,7 +2782,7 @@
       <c r="O39" s="3">
         <v>0</v>
       </c>
-      <c r="T39" s="7">
+      <c r="T39" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -2841,7 +2833,7 @@
       <c r="O40" s="3">
         <v>0</v>
       </c>
-      <c r="T40" s="7">
+      <c r="T40" s="2">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
@@ -2896,7 +2888,7 @@
       <c r="S41" s="3">
         <v>0</v>
       </c>
-      <c r="T41" s="7">
+      <c r="T41" s="2">
         <f t="shared" si="2"/>
         <v>-1</v>
       </c>
@@ -2951,13 +2943,13 @@
       <c r="S42" s="3">
         <v>1</v>
       </c>
-      <c r="T42" s="7">
+      <c r="T42" s="2">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:20">
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D43" s="2">
@@ -3026,7 +3018,7 @@
       </c>
     </row>
     <row r="44" spans="1:20">
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D44" s="2">
@@ -3095,7 +3087,7 @@
       </c>
     </row>
     <row r="45" spans="1:20">
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D45" s="2">
